--- a/artfynd/A 6243-2023 artfynd.xlsx
+++ b/artfynd/A 6243-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6243-2023 artfynd.xlsx
+++ b/artfynd/A 6243-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98473634</v>
+        <v>114554922</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gyttjeå, Nb</t>
+          <t>Norrbotten, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>796511.0921083668</v>
+        <v>796376</v>
       </c>
       <c r="R2" t="n">
-        <v>7335610.783158477</v>
+        <v>7335647</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +764,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98473632</v>
+        <v>114554923</v>
       </c>
       <c r="B3" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +787,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>2387</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gyttjeå, Nb</t>
+          <t>Norrbotten, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>796512.7157123645</v>
+        <v>796340</v>
       </c>
       <c r="R3" t="n">
-        <v>7335610.953283726</v>
+        <v>7335609</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,62 +865,61 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98473633</v>
+        <v>114554924</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gyttjeå, Nb</t>
+          <t>Norrbotten, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>796514.9811805794</v>
+        <v>796393</v>
       </c>
       <c r="R4" t="n">
-        <v>7335612.830268782</v>
+        <v>7335544</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +946,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,66 +966,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114554926</v>
+        <v>98473634</v>
       </c>
       <c r="B5" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrbotten, Nb</t>
+          <t>Gyttjeå, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>796403</v>
+        <v>796511</v>
       </c>
       <c r="R5" t="n">
-        <v>7335669</v>
+        <v>7335611</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,49 +1063,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114554945</v>
+        <v>114554948</v>
       </c>
       <c r="B6" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1161,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>796457</v>
+        <v>796519</v>
       </c>
       <c r="R6" t="n">
-        <v>7335547</v>
+        <v>7335589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,37 +1176,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114554956</v>
+        <v>114554932</v>
       </c>
       <c r="B7" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>796442</v>
+        <v>796447</v>
       </c>
       <c r="R7" t="n">
-        <v>7335524</v>
+        <v>7335522</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114554942</v>
+        <v>114554933</v>
       </c>
       <c r="B8" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1345,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1373,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>796450</v>
+        <v>796446</v>
       </c>
       <c r="R8" t="n">
-        <v>7335512</v>
+        <v>7335513</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,54 +1378,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114554943</v>
+        <v>98473633</v>
       </c>
       <c r="B9" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrbotten, Nb</t>
+          <t>Gyttjeå, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>796458</v>
+        <v>796515</v>
       </c>
       <c r="R9" t="n">
-        <v>7335548</v>
+        <v>7335613</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,12 +1443,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,49 +1463,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114554944</v>
+        <v>114554949</v>
       </c>
       <c r="B10" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1585,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>796464</v>
+        <v>796380</v>
       </c>
       <c r="R10" t="n">
-        <v>7335548</v>
+        <v>7335664</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,15 +1576,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114554948</v>
+        <v>114554950</v>
       </c>
       <c r="B11" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,21 +1587,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>796519</v>
+        <v>796378</v>
       </c>
       <c r="R11" t="n">
-        <v>7335589</v>
+        <v>7335645</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,37 +1677,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114554927</v>
+        <v>114554951</v>
       </c>
       <c r="B12" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1797,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>796386</v>
+        <v>796329</v>
       </c>
       <c r="R12" t="n">
-        <v>7335647</v>
+        <v>7335584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,15 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114554950</v>
+        <v>114554952</v>
       </c>
       <c r="B13" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>796378</v>
+        <v>796367</v>
       </c>
       <c r="R13" t="n">
-        <v>7335645</v>
+        <v>7335571</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,37 +1879,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114554941</v>
+        <v>114554953</v>
       </c>
       <c r="B14" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2009,10 +1918,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>796442</v>
+        <v>796400</v>
       </c>
       <c r="R14" t="n">
-        <v>7335517</v>
+        <v>7335531</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,37 +1980,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114554928</v>
+        <v>114554954</v>
       </c>
       <c r="B15" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2115,10 +2019,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>796377</v>
+        <v>796398</v>
       </c>
       <c r="R15" t="n">
-        <v>7335642</v>
+        <v>7335537</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2177,15 +2081,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114554958</v>
+        <v>114554955</v>
       </c>
       <c r="B16" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2221,10 +2120,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>796457</v>
+        <v>796426</v>
       </c>
       <c r="R16" t="n">
-        <v>7335553</v>
+        <v>7335518</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,15 +2182,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114554949</v>
+        <v>114554956</v>
       </c>
       <c r="B17" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2327,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>796380</v>
+        <v>796442</v>
       </c>
       <c r="R17" t="n">
-        <v>7335664</v>
+        <v>7335524</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,37 +2283,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114554925</v>
+        <v>114554957</v>
       </c>
       <c r="B18" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2433,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>796419</v>
+        <v>796443</v>
       </c>
       <c r="R18" t="n">
-        <v>7335684</v>
+        <v>7335518</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,15 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114554959</v>
+        <v>114554958</v>
       </c>
       <c r="B19" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,10 +2423,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>796467</v>
+        <v>796457</v>
       </c>
       <c r="R19" t="n">
-        <v>7335548</v>
+        <v>7335553</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,37 +2485,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114554922</v>
+        <v>114554959</v>
       </c>
       <c r="B20" t="n">
-        <v>93683</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2645,10 +2524,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>796376</v>
+        <v>796467</v>
       </c>
       <c r="R20" t="n">
-        <v>7335647</v>
+        <v>7335548</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,37 +2586,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114554938</v>
+        <v>114554960</v>
       </c>
       <c r="B21" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2751,10 +2625,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>796444</v>
+        <v>796532</v>
       </c>
       <c r="R21" t="n">
-        <v>7335515</v>
+        <v>7335657</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2813,15 +2687,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>114554918</v>
+        <v>114554935</v>
       </c>
       <c r="B22" t="n">
-        <v>97671</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,21 +2698,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2857,10 +2726,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>796404</v>
+        <v>796330</v>
       </c>
       <c r="R22" t="n">
-        <v>7335672</v>
+        <v>7335584</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,15 +2788,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>114554933</v>
+        <v>114554936</v>
       </c>
       <c r="B23" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2935,21 +2799,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2963,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>796446</v>
+        <v>796399</v>
       </c>
       <c r="R23" t="n">
-        <v>7335513</v>
+        <v>7335532</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3025,15 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>114554932</v>
+        <v>114554937</v>
       </c>
       <c r="B24" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3041,21 +2900,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3069,10 +2928,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>796447</v>
+        <v>796400</v>
       </c>
       <c r="R24" t="n">
-        <v>7335522</v>
+        <v>7335540</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,15 +2990,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>114554946</v>
+        <v>114554938</v>
       </c>
       <c r="B25" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3001,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3175,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>796467</v>
+        <v>796444</v>
       </c>
       <c r="R25" t="n">
-        <v>7335548</v>
+        <v>7335515</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,15 +3091,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>114554934</v>
+        <v>114554939</v>
       </c>
       <c r="B26" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,21 +3102,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3281,10 +3130,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>796447</v>
+        <v>796459</v>
       </c>
       <c r="R26" t="n">
-        <v>7335545</v>
+        <v>7335551</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3343,54 +3192,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>114554957</v>
+        <v>98473632</v>
       </c>
       <c r="B27" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrbotten, Nb</t>
+          <t>Gyttjeå, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>796443</v>
+        <v>796513</v>
       </c>
       <c r="R27" t="n">
-        <v>7335518</v>
+        <v>7335611</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3417,12 +3257,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,27 +3277,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>114554939</v>
+        <v>114554940</v>
       </c>
       <c r="B28" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,21 +3300,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3493,10 +3328,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>796459</v>
+        <v>796368</v>
       </c>
       <c r="R28" t="n">
-        <v>7335551</v>
+        <v>7335572</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3552,6 +3387,1723 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>114554941</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>796442</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7335517</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>114554942</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>796450</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7335512</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>114554943</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>796458</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7335548</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>114554944</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>796464</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7335548</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>114554945</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>796457</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7335547</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>114554946</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>796467</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7335548</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>114554934</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>796447</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7335545</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>114554925</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>796419</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7335684</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>114554926</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>796403</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7335669</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>114554927</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>796386</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7335647</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>114554928</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>796377</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7335642</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>114554929</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>796340</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7335601</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>114554930</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>796335</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7335585</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>114554931</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>796395</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7335545</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>114554920</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>796380</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7335553</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>114554918</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>796404</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7335672</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>114554919</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Norrbotten, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>796340</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7335607</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Ursula Zinko, Mikael Andersson, Anna Eriksson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6243-2023 artfynd.xlsx
+++ b/artfynd/A 6243-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554922</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554923</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554924</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98473634</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554948</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554932</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554933</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98473633</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554949</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1674,6 +1724,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554950</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554951</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554952</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1977,6 +2042,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554953</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2078,6 +2148,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554954</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2179,6 +2254,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554955</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2280,6 +2360,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554956</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2381,6 +2466,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554957</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2482,6 +2572,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554958</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2583,6 +2678,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554959</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2684,6 +2784,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554960</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2785,6 +2890,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554935</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2886,6 +2996,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554936</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2987,6 +3102,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554937</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3088,6 +3208,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554938</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3189,6 +3314,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554939</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3286,6 +3416,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98473632</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3387,6 +3522,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554940</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3488,6 +3628,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554941</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3589,6 +3734,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554942</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3690,6 +3840,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554943</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3791,6 +3946,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554944</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3892,6 +4052,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554945</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3993,6 +4158,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554946</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4094,6 +4264,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554934</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4195,6 +4370,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554925</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4296,6 +4476,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554926</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4397,6 +4582,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554927</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4498,6 +4688,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554928</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4599,6 +4794,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554929</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4700,6 +4900,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554930</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4801,6 +5006,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554931</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4902,6 +5112,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554920</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5003,6 +5218,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554918</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5104,8 +5324,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114554919</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>